--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 PRONGHORN BUCK L.E ARCHERY.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 PRONGHORN BUCK L.E ARCHERY.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -577,10 +577,15 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Average Age Harvested (previous hunting season)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Avg Days Hunted (previous hunting season)</t>
         </is>
@@ -654,10 +659,15 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -734,7 +744,12 @@
           <t>5.2</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
@@ -811,7 +826,12 @@
           <t>3.5</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
@@ -876,7 +896,12 @@
           <t>2.9</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>11.5</t>
         </is>
@@ -953,7 +978,12 @@
           <t>3.4</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
@@ -1030,7 +1060,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
@@ -1107,7 +1142,12 @@
           <t>3.5</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
@@ -1181,10 +1221,15 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
@@ -1254,10 +1299,15 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
@@ -1334,7 +1384,12 @@
           <t>3.6</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -1411,7 +1466,12 @@
           <t>4.7</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
@@ -1485,10 +1545,15 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
@@ -1565,7 +1630,12 @@
           <t>3.6</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
@@ -1639,10 +1709,15 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>4.4</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
@@ -1716,10 +1791,15 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
@@ -1793,10 +1873,15 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1873,7 +1958,12 @@
           <t>4.3</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
@@ -1950,7 +2040,12 @@
           <t>4</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
@@ -2027,7 +2122,12 @@
           <t>5.2</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
@@ -2100,7 +2200,12 @@
           <t>3.5</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -2174,10 +2279,15 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
@@ -2250,7 +2360,12 @@
           <t>4.5</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2312,10 +2427,15 @@
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
@@ -2389,10 +2509,15 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -2466,10 +2591,15 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
           <t>3.4</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>9.3</t>
         </is>
